--- a/output/pdf_financials_xlsx/CAC.P.xlsx
+++ b/output/pdf_financials_xlsx/CAC.P.xlsx
@@ -735,25 +735,25 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.002711</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.014366</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.001485</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.021455</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.082398</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.085566</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.056872</v>
       </c>
     </row>
     <row r="13">
@@ -1191,25 +1191,25 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.152377</v>
+        <v>-0.155088</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.045742</v>
+        <v>-0.060108</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.123665</v>
+        <v>-0.12515</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1.046605</v>
+        <v>1.02515</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.017366</v>
+        <v>-0.06503200000000001</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.022632</v>
+        <v>-0.062934</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.006523</v>
+        <v>-0.06339500000000001</v>
       </c>
     </row>
     <row r="28">
@@ -1247,25 +1247,25 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.152377</v>
+        <v>-0.155088</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.045742</v>
+        <v>-0.060108</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.123665</v>
+        <v>-0.12515</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>1.046605</v>
+        <v>1.02515</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.017366</v>
+        <v>-0.06503200000000001</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.022632</v>
+        <v>-0.062934</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.006523</v>
+        <v>-0.06339500000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1394,25 +1394,25 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.061266</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.050963</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.033306</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.052431</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.038203</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.020853</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.022647</v>
       </c>
     </row>
     <row r="35">
@@ -1450,25 +1450,25 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.902711</v>
+        <v>0.963977</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.867077</v>
+        <v>0.91804</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.771814</v>
+        <v>0.8051199999999999</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>1.760988</v>
+        <v>1.813419</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>1.743382</v>
+        <v>1.781585</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>1.782947</v>
+        <v>1.8038</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>1.763819</v>
+        <v>1.786466</v>
       </c>
     </row>
     <row r="37">
@@ -1786,25 +1786,25 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.07267899999999999</v>
+        <v>0.011413</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.062732</v>
+        <v>0.011769</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.043283</v>
+        <v>0.009977</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.061073</v>
+        <v>0.008642</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.048459</v>
+        <v>0.010256</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.030823</v>
+        <v>0.00997</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.038651</v>
+        <v>0.016004</v>
       </c>
     </row>
     <row r="49">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -7177,7 +7177,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E58" s="5" t="n">

--- a/output/pdf_financials_xlsx/CAC.P.xlsx
+++ b/output/pdf_financials_xlsx/CAC.P.xlsx
@@ -4373,7 +4373,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K103"/>
+  <dimension ref="A1:K108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6247,7 +6247,11 @@
           <t>Deferred tax expense</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>-</t>
@@ -6443,7 +6447,11 @@
           <t>Deferred tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>-</t>
@@ -6594,7 +6602,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>-</t>
@@ -7162,128 +7174,166 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Income</t>
+          <t>Cash flow used in operating activities</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Interest income $</t>
+          <t>Net loss for the period $</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>InterestIncomeNonOperating</t>
+          <t>NetIncomeFromContinuingOperations</t>
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>0.002711</v>
-      </c>
-      <c r="F58" s="5" t="n">
-        <v>0.014366</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>0.001485</v>
-      </c>
-      <c r="H58" s="5" t="n">
-        <v>0.021455</v>
-      </c>
-      <c r="I58" s="5" t="n">
-        <v>0.082398</v>
-      </c>
-      <c r="J58" s="5" t="n">
-        <v>0.085566</v>
-      </c>
-      <c r="K58" s="5" t="n">
-        <v>0.056872</v>
+        <v>-0.152377</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Income</t>
+          <t>Cash flow used in investing activities</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Income total</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Purchase of short-term investments</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>PurchaseOfShortTermInvestments</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="n">
+        <v>-0.9016459999999999</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G59" s="5" t="n">
-        <v>0.001485</v>
-      </c>
-      <c r="H59" s="5" t="n">
-        <v>1.524955</v>
-      </c>
-      <c r="I59" s="5" t="n">
-        <v>0.082398</v>
-      </c>
-      <c r="J59" s="5" t="n">
-        <v>0.085566</v>
-      </c>
-      <c r="K59" s="5" t="n">
-        <v>0.056872</v>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Cash flow used in investing activities</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Annual general and other meetings</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F60" s="5" t="n">
-        <v>0.006975</v>
-      </c>
-      <c r="G60" s="5" t="n">
-        <v>0.011349</v>
-      </c>
-      <c r="H60" s="5" t="n">
-        <v>0.010367</v>
-      </c>
-      <c r="I60" s="5" t="n">
-        <v>0.008629</v>
-      </c>
-      <c r="J60" s="5" t="n">
-        <v>0.008711</v>
-      </c>
-      <c r="K60" s="5" t="n">
-        <v>0.008767</v>
+          <t>Cash flow used in investing activities total</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="n">
+        <v>-0.9016459999999999</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="61">
@@ -7294,39 +7344,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Interest income $</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>0.00306</v>
+        <v>0.002711</v>
       </c>
       <c r="F61" s="5" t="n">
-        <v>0.009180000000000001</v>
+        <v>0.014366</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.009155999999999999</v>
+        <v>0.001485</v>
       </c>
       <c r="H61" s="5" t="n">
-        <v>0.009306999999999999</v>
+        <v>0.021455</v>
       </c>
       <c r="I61" s="5" t="n">
-        <v>0.009639</v>
+        <v>0.082398</v>
       </c>
       <c r="J61" s="5" t="n">
-        <v>0.009639</v>
+        <v>0.085566</v>
       </c>
       <c r="K61" s="5" t="n">
-        <v>0.009639</v>
+        <v>0.056872</v>
       </c>
     </row>
     <row r="62">
@@ -7337,45 +7387,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Office and general</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E62" s="5" t="n">
-        <v>0.000119</v>
+          <t>Income total</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G62" s="5" t="n">
+        <v>0.001485</v>
+      </c>
+      <c r="H62" s="5" t="n">
+        <v>1.524955</v>
       </c>
       <c r="I62" s="5" t="n">
-        <v>0.001751</v>
+        <v>0.082398</v>
       </c>
       <c r="J62" s="5" t="n">
-        <v>0.000665</v>
+        <v>0.085566</v>
       </c>
       <c r="K62" s="5" t="n">
-        <v>0.000704</v>
+        <v>0.056872</v>
       </c>
     </row>
     <row r="63">
@@ -7391,34 +7435,32 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E63" s="5" t="n">
-        <v>0.004906</v>
+          <t>Annual general and other meetings</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F63" s="5" t="n">
-        <v>0.027859</v>
+        <v>0.006975</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.087073</v>
+        <v>0.011349</v>
       </c>
       <c r="H63" s="5" t="n">
-        <v>0.112519</v>
+        <v>0.010367</v>
       </c>
       <c r="I63" s="5" t="n">
-        <v>0.03286</v>
+        <v>0.008629</v>
       </c>
       <c r="J63" s="5" t="n">
-        <v>0.031958</v>
+        <v>0.008711</v>
       </c>
       <c r="K63" s="5" t="n">
-        <v>0.032549</v>
+        <v>0.008767</v>
       </c>
     </row>
     <row r="64">
@@ -7434,40 +7476,34 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Regulatory and filing fees</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="n">
+        <v>0.00306</v>
+      </c>
+      <c r="F64" s="5" t="n">
+        <v>0.009180000000000001</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>0.009155999999999999</v>
+      </c>
+      <c r="H64" s="5" t="n">
+        <v>0.009306999999999999</v>
+      </c>
+      <c r="I64" s="5" t="n">
+        <v>0.009639</v>
       </c>
       <c r="J64" s="5" t="n">
-        <v>0.011961</v>
+        <v>0.009639</v>
       </c>
       <c r="K64" s="5" t="n">
-        <v>0.011736</v>
+        <v>0.009639</v>
       </c>
     </row>
     <row r="65">
@@ -7483,34 +7519,40 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Expenses total</t>
+          <t>Office and general</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>0.155088</v>
-      </c>
-      <c r="F65" s="5" t="n">
-        <v>0.060108</v>
-      </c>
-      <c r="G65" s="5" t="n">
-        <v>0.12515</v>
-      </c>
-      <c r="H65" s="5" t="n">
-        <v>0.47835</v>
+        <v>0.000119</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I65" s="5" t="n">
-        <v>0.06503200000000001</v>
+        <v>0.001751</v>
       </c>
       <c r="J65" s="5" t="n">
-        <v>0.062934</v>
+        <v>0.000665</v>
       </c>
       <c r="K65" s="5" t="n">
-        <v>0.06339500000000001</v>
+        <v>0.000704</v>
       </c>
     </row>
     <row r="66">
@@ -7526,40 +7568,34 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Income (loss) before income taxes</t>
+          <t>Professional fees</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="n">
+        <v>0.004906</v>
+      </c>
+      <c r="F66" s="5" t="n">
+        <v>0.027859</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>-0.123665</v>
+        <v>0.087073</v>
       </c>
       <c r="H66" s="5" t="n">
-        <v>1.046605</v>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.112519</v>
+      </c>
+      <c r="I66" s="5" t="n">
+        <v>0.03286</v>
       </c>
       <c r="J66" s="5" t="n">
-        <v>0.022632</v>
+        <v>0.031958</v>
       </c>
       <c r="K66" s="5" t="n">
-        <v>-0.006523</v>
+        <v>0.032549</v>
       </c>
     </row>
     <row r="67">
@@ -7570,12 +7606,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Income taxes (recovery)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Regulatory and filing fees</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -7594,17 +7630,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H67" s="5" t="n">
-        <v>0.046341</v>
-      </c>
-      <c r="I67" s="5" t="n">
-        <v>-0.001974</v>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J67" s="5" t="n">
-        <v>0.006093</v>
+        <v>0.011961</v>
       </c>
       <c r="K67" s="5" t="n">
-        <v>-0.001635</v>
+        <v>0.011736</v>
       </c>
     </row>
     <row r="68">
@@ -7615,45 +7655,39 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Income taxes (recovery)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Total comprehensive income (loss) for the year $</t>
+          <t>Expenses total</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="n">
+        <v>0.155088</v>
+      </c>
+      <c r="F68" s="5" t="n">
+        <v>0.060108</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>-0.123665</v>
+        <v>0.12515</v>
       </c>
       <c r="H68" s="5" t="n">
-        <v>1.00689</v>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.47835</v>
+      </c>
+      <c r="I68" s="5" t="n">
+        <v>0.06503200000000001</v>
       </c>
       <c r="J68" s="5" t="n">
-        <v>0.016539</v>
+        <v>0.062934</v>
       </c>
       <c r="K68" s="5" t="n">
-        <v>-0.004888</v>
+        <v>0.06339500000000001</v>
       </c>
     </row>
     <row r="69">
@@ -7664,17 +7698,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Income (loss) per share</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Basic and diluted $</t>
+          <t>Income (loss) before income taxes</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>PretaxIncome</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -7687,15 +7721,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G69" s="5" t="n">
+        <v>-0.123665</v>
+      </c>
+      <c r="H69" s="5" t="n">
+        <v>1.046605</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -7703,10 +7733,10 @@
         </is>
       </c>
       <c r="J69" s="5" t="n">
-        <v>1e-09</v>
+        <v>0.022632</v>
       </c>
       <c r="K69" s="5" t="n">
-        <v>0</v>
+        <v>-0.006523</v>
       </c>
     </row>
     <row r="70">
@@ -7717,12 +7747,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Income (loss) per share</t>
+          <t>Income taxes (recovery)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Weighted average shares outstanding (notes</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -7741,21 +7771,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H70" s="5" t="n">
+        <v>0.046341</v>
+      </c>
+      <c r="I70" s="5" t="n">
+        <v>-0.001974</v>
       </c>
       <c r="J70" s="5" t="n">
-        <v>5e-06</v>
+        <v>0.006093</v>
       </c>
       <c r="K70" s="5" t="n">
-        <v>3e-06</v>
+        <v>-0.001635</v>
       </c>
     </row>
     <row r="71">
@@ -7766,17 +7792,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Income (loss) per share</t>
+          <t>Income taxes (recovery)</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Basic and diluted</t>
+          <t>Total comprehensive income (loss) for the year $</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -7789,15 +7815,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G71" s="5" t="n">
+        <v>-0.123665</v>
+      </c>
+      <c r="H71" s="5" t="n">
+        <v>1.00689</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -7805,10 +7827,10 @@
         </is>
       </c>
       <c r="J71" s="5" t="n">
-        <v>16.095</v>
+        <v>0.016539</v>
       </c>
       <c r="K71" s="5" t="n">
-        <v>16.095</v>
+        <v>-0.004888</v>
       </c>
     </row>
     <row r="72">
@@ -7819,15 +7841,19 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Number (#) Amount ($)    account               ($)          Equity ($)</t>
+          <t>Income (loss) per share</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2023 16,095,000 971,226 144,660</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr"/>
+          <t>Basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>
@@ -7854,10 +7880,10 @@
         </is>
       </c>
       <c r="J72" s="5" t="n">
-        <v>1.769013</v>
+        <v>1e-09</v>
       </c>
       <c r="K72" s="5" t="n">
-        <v>0.653127</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -7868,12 +7894,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Total comprehensive income</t>
+          <t>Income (loss) per share</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Total comprehensive income for the year - - -</t>
+          <t>Weighted average shares outstanding (notes</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
@@ -7887,20 +7913,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G73" s="5" t="n">
-        <v>1.00689</v>
-      </c>
-      <c r="H73" s="5" t="n">
-        <v>1.00689</v>
-      </c>
-      <c r="I73" s="5" t="n">
-        <v>0.012714</v>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J73" s="5" t="n">
-        <v>0.016539</v>
+        <v>5e-06</v>
       </c>
       <c r="K73" s="5" t="n">
-        <v>0.016539</v>
+        <v>3e-06</v>
       </c>
     </row>
     <row r="74">
@@ -7911,15 +7943,19 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Total comprehensive income</t>
+          <t>Income (loss) per share</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2024 16,095,000 971,226 144,660</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr"/>
+          <t>Basic and diluted</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>-</t>
@@ -7940,14 +7976,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I74" s="5" t="n">
-        <v>1.785552</v>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J74" s="5" t="n">
-        <v>1.785552</v>
+        <v>16.095</v>
       </c>
       <c r="K74" s="5" t="n">
-        <v>0.669666</v>
+        <v>16.095</v>
       </c>
     </row>
     <row r="75">
@@ -7958,19 +7996,15 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Total comprehensive loss</t>
+          <t>Number (#) Amount ($)    account               ($)          Equity ($)</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Total comprehensive loss for the year - - -</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Balance, December 31, 2023 16,095,000 971,226 144,660</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
           <t>-</t>
@@ -7997,10 +8031,10 @@
         </is>
       </c>
       <c r="J75" s="5" t="n">
-        <v>-0.004888</v>
+        <v>1.769013</v>
       </c>
       <c r="K75" s="5" t="n">
-        <v>-0.004888</v>
+        <v>0.653127</v>
       </c>
     </row>
     <row r="76">
@@ -8011,12 +8045,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Total comprehensive loss</t>
+          <t>Total comprehensive income</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2025 16,095,000 971,226 144,660</t>
+          <t>Total comprehensive income for the year - - -</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -8030,26 +8064,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G76" s="5" t="n">
+        <v>1.00689</v>
+      </c>
+      <c r="H76" s="5" t="n">
+        <v>1.00689</v>
+      </c>
+      <c r="I76" s="5" t="n">
+        <v>0.012714</v>
       </c>
       <c r="J76" s="5" t="n">
-        <v>1.780664</v>
+        <v>0.016539</v>
       </c>
       <c r="K76" s="5" t="n">
-        <v>0.664778</v>
+        <v>0.016539</v>
       </c>
     </row>
     <row r="77">
@@ -8060,41 +8088,43 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Total comprehensive income</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Listing and filing fees</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
-      <c r="E77" s="5" t="n">
-        <v>0.000793</v>
-      </c>
-      <c r="F77" s="5" t="n">
-        <v>0.005344</v>
-      </c>
-      <c r="G77" s="5" t="n">
-        <v>0.010699</v>
-      </c>
-      <c r="H77" s="5" t="n">
-        <v>0.008501999999999999</v>
+          <t>Balance, December 31, 2024 16,095,000 971,226 144,660</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I77" s="5" t="n">
-        <v>0.009410999999999999</v>
+        <v>1.785552</v>
       </c>
       <c r="J77" s="5" t="n">
-        <v>0.009446</v>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.785552</v>
+      </c>
+      <c r="K77" s="5" t="n">
+        <v>0.669666</v>
       </c>
     </row>
     <row r="78">
@@ -8105,37 +8135,49 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Total comprehensive loss</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Regulatory and transfer agency fees</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr"/>
-      <c r="E78" s="5" t="n">
-        <v>0.00155</v>
-      </c>
-      <c r="F78" s="5" t="n">
-        <v>0.006652</v>
-      </c>
-      <c r="G78" s="5" t="n">
-        <v>0.006187</v>
-      </c>
-      <c r="H78" s="5" t="n">
-        <v>0.00404</v>
-      </c>
-      <c r="I78" s="5" t="n">
-        <v>0.002742</v>
+          <t>Total comprehensive loss for the year - - -</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J78" s="5" t="n">
-        <v>0.002515</v>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.004888</v>
+      </c>
+      <c r="K78" s="5" t="n">
+        <v>-0.004888</v>
       </c>
     </row>
     <row r="79">
@@ -8146,19 +8188,15 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Total comprehensive loss</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Income before income taxes</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
+          <t>Balance, December 31, 2025 16,095,000 971,226 144,660</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
           <t>-</t>
@@ -8174,19 +8212,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H79" s="5" t="n">
-        <v>1.046605</v>
-      </c>
-      <c r="I79" s="5" t="n">
-        <v>0.017366</v>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J79" s="5" t="n">
-        <v>0.022632</v>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.780664</v>
+      </c>
+      <c r="K79" s="5" t="n">
+        <v>0.664778</v>
       </c>
     </row>
     <row r="80">
@@ -8197,40 +8237,36 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Income taxes (recovery)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Deferred</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Listing and filing fees</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="n">
+        <v>0.000793</v>
+      </c>
+      <c r="F80" s="5" t="n">
+        <v>0.005344</v>
+      </c>
+      <c r="G80" s="5" t="n">
+        <v>0.010699</v>
       </c>
       <c r="H80" s="5" t="n">
-        <v>-0.006626</v>
+        <v>0.008501999999999999</v>
       </c>
       <c r="I80" s="5" t="n">
-        <v>0.006626</v>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.009410999999999999</v>
+      </c>
+      <c r="J80" s="5" t="n">
+        <v>0.009446</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
@@ -8246,38 +8282,32 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Income taxes (recovery)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Income taxes (recovery) total</t>
+          <t>Regulatory and transfer agency fees</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E81" s="5" t="n">
+        <v>0.00155</v>
+      </c>
+      <c r="F81" s="5" t="n">
+        <v>0.006652</v>
+      </c>
+      <c r="G81" s="5" t="n">
+        <v>0.006187</v>
       </c>
       <c r="H81" s="5" t="n">
-        <v>0.039715</v>
+        <v>0.00404</v>
       </c>
       <c r="I81" s="5" t="n">
-        <v>0.004652</v>
+        <v>0.002742</v>
       </c>
       <c r="J81" s="5" t="n">
-        <v>0.006093</v>
+        <v>0.002515</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
@@ -8293,15 +8323,19 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Income taxes (recovery)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Total comprehensive income for the year $</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr"/>
+          <t>Income before income taxes</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>-</t>
@@ -8318,13 +8352,13 @@
         </is>
       </c>
       <c r="H82" s="5" t="n">
-        <v>1.00689</v>
+        <v>1.046605</v>
       </c>
       <c r="I82" s="5" t="n">
-        <v>0.012714</v>
+        <v>0.017366</v>
       </c>
       <c r="J82" s="5" t="n">
-        <v>0.016539</v>
+        <v>0.022632</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
@@ -8340,19 +8374,15 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Income per share</t>
+          <t>Income taxes (recovery)</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Basic and diluted $</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
           <t>-</t>
@@ -8369,13 +8399,15 @@
         </is>
       </c>
       <c r="H83" s="5" t="n">
-        <v>6.3e-08</v>
+        <v>-0.006626</v>
       </c>
       <c r="I83" s="5" t="n">
-        <v>1e-09</v>
-      </c>
-      <c r="J83" s="5" t="n">
-        <v>1e-09</v>
+        <v>0.006626</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
@@ -8391,12 +8423,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Income per share</t>
+          <t>Income taxes (recovery)</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Weighted average shares outstanding (notes</t>
+          <t>Income taxes (recovery) total</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -8416,13 +8448,13 @@
         </is>
       </c>
       <c r="H84" s="5" t="n">
-        <v>6e-06</v>
+        <v>0.039715</v>
       </c>
       <c r="I84" s="5" t="n">
-        <v>5e-06</v>
+        <v>0.004652</v>
       </c>
       <c r="J84" s="5" t="n">
-        <v>3e-06</v>
+        <v>0.006093</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
@@ -8438,19 +8470,15 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Income per share</t>
+          <t>Income taxes (recovery)</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Basic and diluted</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Total comprehensive income for the year $</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
           <t>-</t>
@@ -8467,13 +8495,13 @@
         </is>
       </c>
       <c r="H85" s="5" t="n">
-        <v>16.095</v>
+        <v>1.00689</v>
       </c>
       <c r="I85" s="5" t="n">
-        <v>16.095</v>
+        <v>0.012714</v>
       </c>
       <c r="J85" s="5" t="n">
-        <v>16.095</v>
+        <v>0.016539</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
@@ -8489,15 +8517,19 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Number (#)  Amount ($)     account              ($)          Equity ($)</t>
+          <t>Income per share</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2022 16,095,000 971,226 144,660</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr"/>
+          <t>Basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>-</t>
@@ -8513,16 +8545,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H86" s="5" t="n">
+        <v>6.3e-08</v>
       </c>
       <c r="I86" s="5" t="n">
-        <v>1.756299</v>
+        <v>1e-09</v>
       </c>
       <c r="J86" s="5" t="n">
-        <v>0.640413</v>
+        <v>1e-09</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
@@ -8538,12 +8568,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Total comprehensive income</t>
+          <t>Income per share</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2023 16,095,000 971,226 144,660</t>
+          <t>Weighted average shares outstanding (notes</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
@@ -8563,13 +8593,13 @@
         </is>
       </c>
       <c r="H87" s="5" t="n">
-        <v>1.769013</v>
+        <v>6e-06</v>
       </c>
       <c r="I87" s="5" t="n">
-        <v>1.769013</v>
+        <v>5e-06</v>
       </c>
       <c r="J87" s="5" t="n">
-        <v>0.653127</v>
+        <v>3e-06</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
@@ -8585,15 +8615,19 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Income</t>
+          <t>Income per share</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Gain on settlement (note 4)</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr"/>
+          <t>Basic and diluted</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
           <t>-</t>
@@ -8610,17 +8644,13 @@
         </is>
       </c>
       <c r="H88" s="5" t="n">
-        <v>1.5035</v>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>16.095</v>
+      </c>
+      <c r="I88" s="5" t="n">
+        <v>16.095</v>
+      </c>
+      <c r="J88" s="5" t="n">
+        <v>16.095</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
@@ -8636,12 +8666,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Number (#)  Amount ($)     account              ($)          Equity ($)</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Travel and related</t>
+          <t>Balance, December 31, 2022 16,095,000 971,226 144,660</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
@@ -8650,24 +8680,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F89" s="5" t="n">
-        <v>0.004098</v>
-      </c>
-      <c r="G89" s="5" t="n">
-        <v>0.000686</v>
-      </c>
-      <c r="H89" s="5" t="n">
-        <v>0.002729</v>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I89" s="5" t="n">
+        <v>1.756299</v>
+      </c>
+      <c r="J89" s="5" t="n">
+        <v>0.640413</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -8683,12 +8715,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Total comprehensive income</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Realized loss on marketable securities (note 13)</t>
+          <t>Balance, December 31, 2023 16,095,000 971,226 144,660</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
@@ -8708,17 +8740,13 @@
         </is>
       </c>
       <c r="H90" s="5" t="n">
-        <v>0.330886</v>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.769013</v>
+      </c>
+      <c r="I90" s="5" t="n">
+        <v>1.769013</v>
+      </c>
+      <c r="J90" s="5" t="n">
+        <v>0.653127</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
@@ -8734,12 +8762,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Share Capital       Option reserve Retained earnings Shareholders’</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2021 16,095,000 971,226 144,660</t>
+          <t>Gain on settlement (note 4)</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
@@ -8759,10 +8787,12 @@
         </is>
       </c>
       <c r="H91" s="5" t="n">
-        <v>0.749409</v>
-      </c>
-      <c r="I91" s="5" t="n">
-        <v>-0.366477</v>
+        <v>1.5035</v>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
@@ -8783,12 +8813,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Total comprehensive income</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2022 16,095,000 971,226 144,660</t>
+          <t>Travel and related</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
@@ -8797,19 +8827,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F92" s="5" t="n">
+        <v>0.004098</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>1.756299</v>
+        <v>0.000686</v>
       </c>
       <c r="H92" s="5" t="n">
-        <v>1.756299</v>
-      </c>
-      <c r="I92" s="5" t="n">
-        <v>0.640413</v>
+        <v>0.002729</v>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
@@ -8835,7 +8865,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Realized loss on marketable securities (note 4)</t>
+          <t>Realized loss on marketable securities (note 13)</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
@@ -8881,19 +8911,15 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Income taxes (recovery)</t>
+          <t>Share Capital       Option reserve Retained earnings Shareholders’</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Income (loss) per share – basic and diluted $</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Balance, December 31, 2021 16,095,000 971,226 144,660</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
           <t>-</t>
@@ -8904,16 +8930,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G94" s="5" t="n">
-        <v>-1.1e-08</v>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H94" s="5" t="n">
-        <v>6.3e-08</v>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.749409</v>
+      </c>
+      <c r="I94" s="5" t="n">
+        <v>-0.366477</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
@@ -8934,12 +8960,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Weighted average shares outstanding – basic and</t>
+          <t>Total comprehensive income</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Weighted average shares outstanding – basic and diluted (notes 3, 7)</t>
+          <t>Balance, December 31, 2022 16,095,000 971,226 144,660</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
@@ -8954,15 +8980,13 @@
         </is>
       </c>
       <c r="G95" s="5" t="n">
-        <v>11.327877</v>
+        <v>1.756299</v>
       </c>
       <c r="H95" s="5" t="n">
-        <v>16.095</v>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.756299</v>
+      </c>
+      <c r="I95" s="5" t="n">
+        <v>0.640413</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
@@ -8983,12 +9007,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Share Capital       Option reserve Retained earnings Shareholders’</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2020 16,095,000 971,226 144,660</t>
+          <t>Realized loss on marketable securities (note 4)</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -9002,11 +9026,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G96" s="5" t="n">
-        <v>0.873074</v>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H96" s="5" t="n">
-        <v>-0.242812</v>
+        <v>0.330886</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -9032,17 +9058,17 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Total comprehensive loss for the</t>
+          <t>Income taxes (recovery)</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Total comprehensive loss for the year - - -</t>
+          <t>Income (loss) per share – basic and diluted $</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -9056,10 +9082,10 @@
         </is>
       </c>
       <c r="G97" s="5" t="n">
-        <v>-0.123665</v>
+        <v>-1.1e-08</v>
       </c>
       <c r="H97" s="5" t="n">
-        <v>-0.123665</v>
+        <v>6.3e-08</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -9085,12 +9111,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Total comprehensive loss for the</t>
+          <t>Weighted average shares outstanding – basic and</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2021 16,095,000 971,226 144,660</t>
+          <t>Weighted average shares outstanding – basic and diluted (notes 3, 7)</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
@@ -9105,10 +9131,10 @@
         </is>
       </c>
       <c r="G98" s="5" t="n">
-        <v>0.749409</v>
+        <v>11.327877</v>
       </c>
       <c r="H98" s="5" t="n">
-        <v>-0.366477</v>
+        <v>16.095</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -9134,30 +9160,30 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>For the period from</t>
+          <t>Share Capital       Option reserve Retained earnings Shareholders’</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>December 31, 2019 December</t>
+          <t>Balance, December 31, 2020 16,095,000 971,226 144,660</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
-      <c r="E99" s="5" t="n">
-        <v>0.002018</v>
-      </c>
-      <c r="F99" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G99" s="5" t="n">
+        <v>0.873074</v>
+      </c>
+      <c r="H99" s="5" t="n">
+        <v>-0.242812</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -9183,32 +9209,34 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Total comprehensive loss for the</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Stock-based compensation</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr"/>
-      <c r="E100" s="5" t="n">
-        <v>0.14466</v>
+          <t>Total comprehensive loss for the year - - -</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G100" s="5" t="n">
+        <v>-0.123665</v>
+      </c>
+      <c r="H100" s="5" t="n">
+        <v>-0.123665</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -9234,34 +9262,30 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Total comprehensive loss for the</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Total comprehensive loss for the period $</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E101" s="5" t="n">
-        <v>-0.152377</v>
-      </c>
-      <c r="F101" s="5" t="n">
-        <v>-0.045742</v>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Balance, December 31, 2021 16,095,000 971,226 144,660</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G101" s="5" t="n">
+        <v>0.749409</v>
+      </c>
+      <c r="H101" s="5" t="n">
+        <v>-0.366477</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -9287,24 +9311,20 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>For the period from</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Loss per share – basic and diluted $</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>December 31, 2019 December</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
       <c r="E102" s="5" t="n">
-        <v>-1.23e-07</v>
+        <v>0.002018</v>
       </c>
       <c r="F102" s="5" t="n">
-        <v>-8e-09</v>
+        <v>3.1e-05</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -9340,42 +9360,307 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Weighted average shares outstanding – basic and</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Weighted average shares outstanding – basic and diluted (note 5)</t>
+          <t>Stock-based compensation</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" s="5" t="n">
+        <v>0.14466</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Total comprehensive loss for the period $</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E104" s="5" t="n">
+        <v>-0.152377</v>
+      </c>
+      <c r="F104" s="5" t="n">
+        <v>-0.045742</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Loss per share – basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E105" s="5" t="n">
+        <v>-1.23e-07</v>
+      </c>
+      <c r="F105" s="5" t="n">
+        <v>-8e-09</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Weighted average shares outstanding – basic and</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Weighted average shares outstanding – basic and diluted (note 5)</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" s="5" t="n">
         <v>1.240262</v>
       </c>
-      <c r="F103" s="5" t="n">
+      <c r="F106" s="5" t="n">
         <v>6.095</v>
       </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr">
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Weighted average shares outstanding</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>basic and diluted (note 5)</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" s="5" t="n">
+        <v>1.240262</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
         <is>
           <t>-</t>
         </is>
